--- a/who-ddcc-map-sct-ichi-specimen-origin.xlsx
+++ b/who-ddcc-map-sct-ichi-specimen-origin.xlsx
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>WHO (http://who.int)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
